--- a/docs/template/Project_Work Breakdown Structure.xlsx
+++ b/docs/template/Project_Work Breakdown Structure.xlsx
@@ -15,11 +15,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="m&quot;/&quot;d;@"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <charset val="129"/>
@@ -83,8 +85,23 @@
       <color rgb="FF5B9BD5"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="00004085"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -137,8 +154,26 @@
         <fgColor rgb="FF5B9BD5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CCE5FF"/>
+        <bgColor rgb="00CCE5FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="32">
+  <borders count="33">
     <border>
       <left/>
       <right/>
@@ -533,13 +568,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D0D0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -706,6 +755,57 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1104,7 +1204,7 @@
     <row r="2" ht="18" customHeight="1" s="64" thickBot="1">
       <c r="B2" s="16" t="inlineStr">
         <is>
-          <t>Project Work Breakdown Structure (WBS)</t>
+          <t>TrafficVision – Work Breakdown Structure (WBS)</t>
         </is>
       </c>
       <c r="C2" s="17" t="n"/>
@@ -1118,7 +1218,7 @@
       <c r="E3" s="1" t="n"/>
       <c r="J3" s="23" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1229,7 @@
       <c r="E4" s="1" t="n"/>
       <c r="J4" s="23" t="inlineStr">
         <is>
-          <t>In-progress</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1240,7 @@
       <c r="E5" s="1" t="n"/>
       <c r="J5" s="23" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>Chậm / cần xử lý</t>
         </is>
       </c>
     </row>
@@ -1153,11 +1253,12 @@
           <t>Today</t>
         </is>
       </c>
-      <c r="C7" s="21" t="n"/>
+      <c r="C7" s="66" t="n">
+        <v>46298</v>
+      </c>
       <c r="D7" s="20" t="n"/>
-      <c r="E7" s="27">
-        <f>TODAY()</f>
-        <v/>
+      <c r="E7" s="27" t="n">
+        <v>46298</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="64" thickBot="1">
@@ -1166,7 +1267,11 @@
           <t>Project Team Name</t>
         </is>
       </c>
-      <c r="C8" s="21" t="n"/>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>TrafficVision</t>
+        </is>
+      </c>
       <c r="D8" s="20" t="n"/>
       <c r="E8" s="28" t="n"/>
     </row>
@@ -1176,7 +1281,11 @@
           <t>Project Topic</t>
         </is>
       </c>
-      <c r="C9" s="56" t="n"/>
+      <c r="C9" s="56" t="inlineStr">
+        <is>
+          <t>TrafficVision – Hệ thống nhận dạng biển báo giao thông Việt Nam bằng AI</t>
+        </is>
+      </c>
       <c r="D9" s="65" t="n"/>
       <c r="E9" s="28" t="n"/>
     </row>
@@ -1371,676 +1480,1141 @@
       <c r="H13" s="45" t="n"/>
       <c r="I13" s="45" t="n"/>
       <c r="J13" s="63" t="n"/>
-      <c r="K13" s="26" t="n">
-        <v>44501</v>
-      </c>
-      <c r="L13" s="24" t="n">
-        <v>44502</v>
-      </c>
-      <c r="M13" s="24" t="n">
-        <v>44503</v>
-      </c>
-      <c r="N13" s="24" t="n">
-        <v>44504</v>
-      </c>
-      <c r="O13" s="24" t="n">
-        <v>44505</v>
-      </c>
-      <c r="P13" s="24" t="n">
-        <v>44506</v>
-      </c>
-      <c r="Q13" s="24" t="n">
-        <v>44507</v>
-      </c>
-      <c r="R13" s="24" t="n">
-        <v>44508</v>
-      </c>
-      <c r="S13" s="24" t="n">
-        <v>44509</v>
-      </c>
-      <c r="T13" s="24" t="n">
-        <v>44510</v>
-      </c>
-      <c r="U13" s="24" t="n">
-        <v>44511</v>
-      </c>
-      <c r="V13" s="24" t="n">
-        <v>44512</v>
-      </c>
-      <c r="W13" s="24" t="n">
-        <v>44513</v>
-      </c>
-      <c r="X13" s="24" t="n">
-        <v>44514</v>
-      </c>
-      <c r="Y13" s="24" t="n">
-        <v>44515</v>
-      </c>
-      <c r="Z13" s="24" t="n">
-        <v>44516</v>
-      </c>
-      <c r="AA13" s="24" t="n">
-        <v>44517</v>
-      </c>
-      <c r="AB13" s="24" t="n">
-        <v>44518</v>
-      </c>
-      <c r="AC13" s="24" t="n">
-        <v>44519</v>
-      </c>
-      <c r="AD13" s="25" t="n">
-        <v>44520</v>
+      <c r="K13" s="67" t="n">
+        <v>46293</v>
+      </c>
+      <c r="L13" s="68" t="n">
+        <v>46294</v>
+      </c>
+      <c r="M13" s="68" t="n">
+        <v>46295</v>
+      </c>
+      <c r="N13" s="68" t="n">
+        <v>46296</v>
+      </c>
+      <c r="O13" s="68" t="n">
+        <v>46297</v>
+      </c>
+      <c r="P13" s="68" t="n">
+        <v>46300</v>
+      </c>
+      <c r="Q13" s="68" t="n">
+        <v>46301</v>
+      </c>
+      <c r="R13" s="68" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S13" s="68" t="n">
+        <v>46303</v>
+      </c>
+      <c r="T13" s="68" t="n">
+        <v>46304</v>
+      </c>
+      <c r="U13" s="68" t="n">
+        <v>46307</v>
+      </c>
+      <c r="V13" s="68" t="n">
+        <v>46308</v>
+      </c>
+      <c r="W13" s="68" t="n">
+        <v>46309</v>
+      </c>
+      <c r="X13" s="68" t="n">
+        <v>46310</v>
+      </c>
+      <c r="Y13" s="68" t="n">
+        <v>46311</v>
+      </c>
+      <c r="Z13" s="68" t="n">
+        <v>46314</v>
+      </c>
+      <c r="AA13" s="68" t="n">
+        <v>46315</v>
+      </c>
+      <c r="AB13" s="68" t="n">
+        <v>46316</v>
+      </c>
+      <c r="AC13" s="68" t="n">
+        <v>46317</v>
+      </c>
+      <c r="AD13" s="69" t="n">
+        <v>46318</v>
       </c>
     </row>
     <row r="14" ht="42" customHeight="1" s="64">
-      <c r="B14" s="36" t="inlineStr">
-        <is>
-          <t>1. Title</t>
-        </is>
-      </c>
-      <c r="C14" s="31" t="n"/>
-      <c r="D14" s="31" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="6">
-        <f>TODAY()</f>
-        <v/>
-      </c>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="9" t="n"/>
-      <c r="I14" s="33" t="n"/>
-      <c r="J14" s="7" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="K14" s="37" t="n"/>
-      <c r="L14" s="38" t="n"/>
-      <c r="M14" s="38" t="n"/>
-      <c r="N14" s="38" t="n"/>
-      <c r="O14" s="38" t="n"/>
-      <c r="P14" s="31" t="n"/>
-      <c r="Q14" s="31" t="n"/>
-      <c r="R14" s="31" t="n"/>
-      <c r="S14" s="31" t="n"/>
-      <c r="T14" s="31" t="n"/>
-      <c r="U14" s="31" t="n"/>
-      <c r="V14" s="31" t="n"/>
-      <c r="W14" s="31" t="n"/>
-      <c r="X14" s="31" t="n"/>
-      <c r="Y14" s="31" t="n"/>
-      <c r="Z14" s="31" t="n"/>
-      <c r="AA14" s="31" t="n"/>
-      <c r="AB14" s="31" t="n"/>
-      <c r="AC14" s="31" t="n"/>
-      <c r="AD14" s="8" t="n"/>
+      <c r="B14" s="70" t="inlineStr">
+        <is>
+          <t>US-01 – Kiến trúc ứng dụng baseline và Model Registry</t>
+        </is>
+      </c>
+      <c r="C14" s="71" t="n"/>
+      <c r="D14" s="71" t="n"/>
+      <c r="E14" s="72" t="n"/>
+      <c r="F14" s="73" t="n">
+        <v>46292</v>
+      </c>
+      <c r="G14" s="73" t="n">
+        <v>46293</v>
+      </c>
+      <c r="H14" s="74" t="inlineStr">
+        <is>
+          <t>Nam + Điệp</t>
+        </is>
+      </c>
+      <c r="I14" s="75" t="inlineStr">
+        <is>
+          <t>Baseline ONNX CPU, manifest.json, production</t>
+        </is>
+      </c>
+      <c r="J14" s="76" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
+        </is>
+      </c>
+      <c r="K14" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" s="78" t="n"/>
+      <c r="N14" s="78" t="n"/>
+      <c r="O14" s="78" t="n"/>
+      <c r="P14" s="71" t="n"/>
+      <c r="Q14" s="71" t="n"/>
+      <c r="R14" s="71" t="n"/>
+      <c r="S14" s="71" t="n"/>
+      <c r="T14" s="71" t="n"/>
+      <c r="U14" s="71" t="n"/>
+      <c r="V14" s="71" t="n"/>
+      <c r="W14" s="71" t="n"/>
+      <c r="X14" s="71" t="n"/>
+      <c r="Y14" s="71" t="n"/>
+      <c r="Z14" s="71" t="n"/>
+      <c r="AA14" s="71" t="n"/>
+      <c r="AB14" s="71" t="n"/>
+      <c r="AC14" s="71" t="n"/>
+      <c r="AD14" s="71" t="n"/>
     </row>
     <row r="15" ht="42" customHeight="1" s="64">
-      <c r="B15" s="30" t="n"/>
-      <c r="C15" s="31" t="inlineStr">
-        <is>
-          <t>1.1. Sub-title</t>
-        </is>
-      </c>
-      <c r="D15" s="31" t="n"/>
-      <c r="E15" s="31" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="9" t="n"/>
-      <c r="I15" s="33" t="n"/>
-      <c r="J15" s="7" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="K15" s="39" t="n"/>
-      <c r="L15" s="40" t="n"/>
-      <c r="M15" s="31" t="n"/>
-      <c r="N15" s="31" t="n"/>
-      <c r="O15" s="31" t="n"/>
-      <c r="P15" s="31" t="n"/>
-      <c r="Q15" s="31" t="n"/>
-      <c r="R15" s="31" t="n"/>
-      <c r="S15" s="31" t="n"/>
-      <c r="T15" s="31" t="n"/>
-      <c r="U15" s="31" t="n"/>
-      <c r="V15" s="31" t="n"/>
-      <c r="W15" s="31" t="n"/>
-      <c r="X15" s="31" t="n"/>
-      <c r="Y15" s="31" t="n"/>
-      <c r="Z15" s="31" t="n"/>
-      <c r="AA15" s="31" t="n"/>
-      <c r="AB15" s="31" t="n"/>
-      <c r="AC15" s="31" t="n"/>
-      <c r="AD15" s="8" t="n"/>
+      <c r="B15" s="71" t="n"/>
+      <c r="C15" s="79" t="inlineStr">
+        <is>
+          <t>US-01.01 – Bootstrap mô hình baseline YOLO11n ONNX</t>
+        </is>
+      </c>
+      <c r="D15" s="71" t="n"/>
+      <c r="E15" s="71" t="n"/>
+      <c r="F15" s="73" t="n">
+        <v>46292</v>
+      </c>
+      <c r="G15" s="73" t="n">
+        <v>46292</v>
+      </c>
+      <c r="H15" s="74" t="inlineStr">
+        <is>
+          <t>Nam</t>
+        </is>
+      </c>
+      <c r="I15" s="75" t="inlineStr">
+        <is>
+          <t>Baseline COCO + SHA-256 + ModelRegistry</t>
+        </is>
+      </c>
+      <c r="J15" s="76" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
+        </is>
+      </c>
+      <c r="K15" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L15" s="80" t="n"/>
+      <c r="M15" s="71" t="n"/>
+      <c r="N15" s="71" t="n"/>
+      <c r="O15" s="71" t="n"/>
+      <c r="P15" s="71" t="n"/>
+      <c r="Q15" s="71" t="n"/>
+      <c r="R15" s="71" t="n"/>
+      <c r="S15" s="71" t="n"/>
+      <c r="T15" s="71" t="n"/>
+      <c r="U15" s="71" t="n"/>
+      <c r="V15" s="71" t="n"/>
+      <c r="W15" s="71" t="n"/>
+      <c r="X15" s="71" t="n"/>
+      <c r="Y15" s="71" t="n"/>
+      <c r="Z15" s="71" t="n"/>
+      <c r="AA15" s="71" t="n"/>
+      <c r="AB15" s="71" t="n"/>
+      <c r="AC15" s="71" t="n"/>
+      <c r="AD15" s="71" t="n"/>
     </row>
     <row r="16" ht="42" customHeight="1" s="64">
-      <c r="B16" s="30" t="n"/>
-      <c r="C16" s="31" t="n"/>
-      <c r="D16" s="31" t="inlineStr">
-        <is>
-          <t>1.1.1. Sub-title</t>
-        </is>
-      </c>
-      <c r="E16" s="31" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="9" t="n"/>
-      <c r="I16" s="33" t="n"/>
-      <c r="J16" s="7" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="K16" s="30" t="n"/>
-      <c r="L16" s="40" t="n"/>
-      <c r="M16" s="40" t="n"/>
-      <c r="N16" s="40" t="n"/>
-      <c r="O16" s="31" t="n"/>
-      <c r="P16" s="31" t="n"/>
-      <c r="Q16" s="31" t="n"/>
-      <c r="R16" s="31" t="n"/>
-      <c r="S16" s="31" t="n"/>
-      <c r="T16" s="31" t="n"/>
-      <c r="U16" s="31" t="n"/>
-      <c r="V16" s="31" t="n"/>
-      <c r="W16" s="31" t="n"/>
-      <c r="X16" s="31" t="n"/>
-      <c r="Y16" s="31" t="n"/>
-      <c r="Z16" s="31" t="n"/>
-      <c r="AA16" s="31" t="n"/>
-      <c r="AB16" s="31" t="n"/>
-      <c r="AC16" s="31" t="n"/>
-      <c r="AD16" s="8" t="n"/>
+      <c r="B16" s="71" t="n"/>
+      <c r="C16" s="71" t="n"/>
+      <c r="D16" s="79" t="inlineStr">
+        <is>
+          <t>US-01.02 – Xây dựng pipeline suy luận ảnh/video và SQLite</t>
+        </is>
+      </c>
+      <c r="E16" s="71" t="n"/>
+      <c r="F16" s="73" t="n">
+        <v>46292</v>
+      </c>
+      <c r="G16" s="73" t="n">
+        <v>46293</v>
+      </c>
+      <c r="H16" s="74" t="inlineStr">
+        <is>
+          <t>Điệp</t>
+        </is>
+      </c>
+      <c r="I16" s="75" t="inlineStr">
+        <is>
+          <t>Ảnh/video chú thích, CSV thống kê, CSDL SQLite</t>
+        </is>
+      </c>
+      <c r="J16" s="76" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
+        </is>
+      </c>
+      <c r="K16" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L16" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" s="80" t="n"/>
+      <c r="N16" s="80" t="n"/>
+      <c r="O16" s="71" t="n"/>
+      <c r="P16" s="71" t="n"/>
+      <c r="Q16" s="71" t="n"/>
+      <c r="R16" s="71" t="n"/>
+      <c r="S16" s="71" t="n"/>
+      <c r="T16" s="71" t="n"/>
+      <c r="U16" s="71" t="n"/>
+      <c r="V16" s="71" t="n"/>
+      <c r="W16" s="71" t="n"/>
+      <c r="X16" s="71" t="n"/>
+      <c r="Y16" s="71" t="n"/>
+      <c r="Z16" s="71" t="n"/>
+      <c r="AA16" s="71" t="n"/>
+      <c r="AB16" s="71" t="n"/>
+      <c r="AC16" s="71" t="n"/>
+      <c r="AD16" s="71" t="n"/>
     </row>
     <row r="17" ht="42" customHeight="1" s="64">
-      <c r="B17" s="30" t="n"/>
-      <c r="C17" s="31" t="n"/>
-      <c r="D17" s="31" t="n"/>
-      <c r="E17" s="31" t="inlineStr">
-        <is>
-          <t>1.1.1.1. Sub-title</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="n"/>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="9" t="n"/>
-      <c r="I17" s="33" t="n"/>
-      <c r="J17" s="7" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="K17" s="30" t="n"/>
-      <c r="L17" s="31" t="n"/>
-      <c r="M17" s="31" t="n"/>
-      <c r="N17" s="40" t="n"/>
-      <c r="O17" s="40" t="n"/>
-      <c r="P17" s="31" t="n"/>
-      <c r="Q17" s="31" t="n"/>
-      <c r="R17" s="31" t="n"/>
-      <c r="S17" s="31" t="n"/>
-      <c r="T17" s="31" t="n"/>
-      <c r="U17" s="31" t="n"/>
-      <c r="V17" s="31" t="n"/>
-      <c r="W17" s="31" t="n"/>
-      <c r="X17" s="31" t="n"/>
-      <c r="Y17" s="31" t="n"/>
-      <c r="Z17" s="31" t="n"/>
-      <c r="AA17" s="31" t="n"/>
-      <c r="AB17" s="31" t="n"/>
-      <c r="AC17" s="31" t="n"/>
-      <c r="AD17" s="8" t="n"/>
+      <c r="B17" s="71" t="n"/>
+      <c r="C17" s="71" t="n"/>
+      <c r="D17" s="71" t="n"/>
+      <c r="E17" s="79" t="inlineStr">
+        <is>
+          <t>US-01.03 – Giao diện Streamlit đa tab &amp; Cảnh báo baseline</t>
+        </is>
+      </c>
+      <c r="F17" s="73" t="n">
+        <v>46292</v>
+      </c>
+      <c r="G17" s="73" t="n">
+        <v>46293</v>
+      </c>
+      <c r="H17" s="74" t="inlineStr">
+        <is>
+          <t>Điệp + Nam</t>
+        </is>
+      </c>
+      <c r="I17" s="75" t="inlineStr">
+        <is>
+          <t>6 trang web Streamlit; cảnh báo baseline; settings</t>
+        </is>
+      </c>
+      <c r="J17" s="76" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
+        </is>
+      </c>
+      <c r="K17" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L17" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" s="71" t="n"/>
+      <c r="N17" s="80" t="n"/>
+      <c r="O17" s="80" t="n"/>
+      <c r="P17" s="71" t="n"/>
+      <c r="Q17" s="71" t="n"/>
+      <c r="R17" s="71" t="n"/>
+      <c r="S17" s="71" t="n"/>
+      <c r="T17" s="71" t="n"/>
+      <c r="U17" s="71" t="n"/>
+      <c r="V17" s="71" t="n"/>
+      <c r="W17" s="71" t="n"/>
+      <c r="X17" s="71" t="n"/>
+      <c r="Y17" s="71" t="n"/>
+      <c r="Z17" s="71" t="n"/>
+      <c r="AA17" s="71" t="n"/>
+      <c r="AB17" s="71" t="n"/>
+      <c r="AC17" s="71" t="n"/>
+      <c r="AD17" s="71" t="n"/>
     </row>
     <row r="18" ht="42" customHeight="1" s="64">
-      <c r="B18" s="36" t="n"/>
-      <c r="C18" s="31" t="n"/>
-      <c r="D18" s="31" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="6" t="n"/>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="9" t="n"/>
-      <c r="I18" s="33" t="n"/>
-      <c r="J18" s="7" t="inlineStr">
-        <is>
-          <t>In-progress</t>
-        </is>
-      </c>
-      <c r="K18" s="30" t="n"/>
-      <c r="L18" s="31" t="n"/>
-      <c r="M18" s="31" t="n"/>
-      <c r="N18" s="31" t="n"/>
-      <c r="O18" s="31" t="n"/>
-      <c r="P18" s="38" t="n"/>
-      <c r="Q18" s="38" t="n"/>
-      <c r="R18" s="38" t="n"/>
-      <c r="S18" s="38" t="n"/>
-      <c r="T18" s="38" t="n"/>
-      <c r="U18" s="38" t="n"/>
-      <c r="V18" s="38" t="n"/>
-      <c r="W18" s="38" t="n"/>
-      <c r="X18" s="38" t="n"/>
-      <c r="Y18" s="38" t="n"/>
-      <c r="Z18" s="31" t="n"/>
-      <c r="AA18" s="31" t="n"/>
-      <c r="AB18" s="31" t="n"/>
-      <c r="AC18" s="31" t="n"/>
-      <c r="AD18" s="8" t="n"/>
+      <c r="B18" s="70" t="inlineStr">
+        <is>
+          <t>US-02 – Dữ liệu 82 lớp biển báo VN và Quality Gate</t>
+        </is>
+      </c>
+      <c r="C18" s="71" t="n"/>
+      <c r="D18" s="71" t="n"/>
+      <c r="E18" s="72" t="n"/>
+      <c r="F18" s="73" t="n">
+        <v>46293</v>
+      </c>
+      <c r="G18" s="73" t="n">
+        <v>46294</v>
+      </c>
+      <c r="H18" s="74" t="inlineStr">
+        <is>
+          <t>Vân Anh + Nghị</t>
+        </is>
+      </c>
+      <c r="I18" s="75" t="inlineStr">
+        <is>
+          <t>Catalog QCVN 41, Quality Gate, Snapshot, EDA</t>
+        </is>
+      </c>
+      <c r="J18" s="76" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
+        </is>
+      </c>
+      <c r="K18" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L18" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N18" s="71" t="n"/>
+      <c r="O18" s="71" t="n"/>
+      <c r="P18" s="78" t="n"/>
+      <c r="Q18" s="78" t="n"/>
+      <c r="R18" s="78" t="n"/>
+      <c r="S18" s="78" t="n"/>
+      <c r="T18" s="78" t="n"/>
+      <c r="U18" s="78" t="n"/>
+      <c r="V18" s="78" t="n"/>
+      <c r="W18" s="78" t="n"/>
+      <c r="X18" s="78" t="n"/>
+      <c r="Y18" s="78" t="n"/>
+      <c r="Z18" s="71" t="n"/>
+      <c r="AA18" s="71" t="n"/>
+      <c r="AB18" s="71" t="n"/>
+      <c r="AC18" s="71" t="n"/>
+      <c r="AD18" s="71" t="n"/>
     </row>
     <row r="19" ht="42" customHeight="1" s="64">
-      <c r="B19" s="30" t="n"/>
-      <c r="C19" s="31" t="n"/>
-      <c r="D19" s="31" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="6" t="n"/>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="9" t="n"/>
-      <c r="I19" s="33" t="n"/>
-      <c r="J19" s="7" t="inlineStr">
-        <is>
-          <t>In-progress</t>
-        </is>
-      </c>
-      <c r="K19" s="30" t="n"/>
-      <c r="L19" s="31" t="n"/>
-      <c r="M19" s="31" t="n"/>
-      <c r="N19" s="31" t="n"/>
-      <c r="O19" s="31" t="n"/>
-      <c r="P19" s="40" t="n"/>
-      <c r="Q19" s="40" t="n"/>
-      <c r="R19" s="31" t="n"/>
-      <c r="S19" s="31" t="n"/>
-      <c r="T19" s="31" t="n"/>
-      <c r="U19" s="31" t="n"/>
-      <c r="V19" s="31" t="n"/>
-      <c r="W19" s="31" t="n"/>
-      <c r="X19" s="31" t="n"/>
-      <c r="Y19" s="31" t="n"/>
-      <c r="Z19" s="31" t="n"/>
-      <c r="AA19" s="31" t="n"/>
-      <c r="AB19" s="31" t="n"/>
-      <c r="AC19" s="31" t="n"/>
-      <c r="AD19" s="8" t="n"/>
+      <c r="B19" s="71" t="n"/>
+      <c r="C19" s="79" t="inlineStr">
+        <is>
+          <t>US-02.01 – Chuẩn hóa danh mục 82 lớp và nạp dữ liệu</t>
+        </is>
+      </c>
+      <c r="D19" s="71" t="n"/>
+      <c r="E19" s="72" t="n"/>
+      <c r="F19" s="73" t="n">
+        <v>46293</v>
+      </c>
+      <c r="G19" s="73" t="n">
+        <v>46293</v>
+      </c>
+      <c r="H19" s="74" t="inlineStr">
+        <is>
+          <t>Vân Anh</t>
+        </is>
+      </c>
+      <c r="I19" s="75" t="inlineStr">
+        <is>
+          <t>Catalog 82 lớp VN, nạp train/val/test split</t>
+        </is>
+      </c>
+      <c r="J19" s="76" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
+        </is>
+      </c>
+      <c r="K19" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L19" s="71" t="n"/>
+      <c r="M19" s="71" t="n"/>
+      <c r="N19" s="71" t="n"/>
+      <c r="O19" s="71" t="n"/>
+      <c r="P19" s="80" t="n"/>
+      <c r="Q19" s="80" t="n"/>
+      <c r="R19" s="71" t="n"/>
+      <c r="S19" s="71" t="n"/>
+      <c r="T19" s="71" t="n"/>
+      <c r="U19" s="71" t="n"/>
+      <c r="V19" s="71" t="n"/>
+      <c r="W19" s="71" t="n"/>
+      <c r="X19" s="71" t="n"/>
+      <c r="Y19" s="71" t="n"/>
+      <c r="Z19" s="71" t="n"/>
+      <c r="AA19" s="71" t="n"/>
+      <c r="AB19" s="71" t="n"/>
+      <c r="AC19" s="71" t="n"/>
+      <c r="AD19" s="71" t="n"/>
     </row>
     <row r="20" ht="42" customHeight="1" s="64">
-      <c r="B20" s="30" t="n"/>
-      <c r="C20" s="31" t="n"/>
-      <c r="D20" s="31" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="6" t="n"/>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="9" t="n"/>
-      <c r="I20" s="33" t="n"/>
-      <c r="J20" s="7" t="inlineStr">
-        <is>
-          <t>In-progress</t>
-        </is>
-      </c>
-      <c r="K20" s="30" t="n"/>
-      <c r="L20" s="31" t="n"/>
-      <c r="M20" s="31" t="n"/>
-      <c r="N20" s="31" t="n"/>
-      <c r="O20" s="31" t="n"/>
-      <c r="P20" s="31" t="n"/>
-      <c r="Q20" s="31" t="n"/>
-      <c r="R20" s="40" t="n"/>
-      <c r="S20" s="40" t="n"/>
-      <c r="T20" s="40" t="n"/>
-      <c r="U20" s="31" t="n"/>
-      <c r="V20" s="31" t="n"/>
-      <c r="W20" s="31" t="n"/>
-      <c r="X20" s="31" t="n"/>
-      <c r="Y20" s="31" t="n"/>
-      <c r="Z20" s="31" t="n"/>
-      <c r="AA20" s="31" t="n"/>
-      <c r="AB20" s="31" t="n"/>
-      <c r="AC20" s="31" t="n"/>
-      <c r="AD20" s="8" t="n"/>
+      <c r="B20" s="71" t="n"/>
+      <c r="C20" s="71" t="n"/>
+      <c r="D20" s="79" t="inlineStr">
+        <is>
+          <t>US-02.02 – Cổng Quality Gate 5 tiêu chí &amp; Dataset Repair</t>
+        </is>
+      </c>
+      <c r="E20" s="72" t="n"/>
+      <c r="F20" s="73" t="n">
+        <v>46293</v>
+      </c>
+      <c r="G20" s="73" t="n">
+        <v>46294</v>
+      </c>
+      <c r="H20" s="74" t="inlineStr">
+        <is>
+          <t>Vân Anh</t>
+        </is>
+      </c>
+      <c r="I20" s="75" t="inlineStr">
+        <is>
+          <t>Quality Gate 5 tiêu chí chặn rác, script repair.py</t>
+        </is>
+      </c>
+      <c r="J20" s="76" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
+        </is>
+      </c>
+      <c r="K20" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L20" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" s="71" t="n"/>
+      <c r="N20" s="71" t="n"/>
+      <c r="O20" s="71" t="n"/>
+      <c r="P20" s="71" t="n"/>
+      <c r="Q20" s="71" t="n"/>
+      <c r="R20" s="80" t="n"/>
+      <c r="S20" s="80" t="n"/>
+      <c r="T20" s="80" t="n"/>
+      <c r="U20" s="71" t="n"/>
+      <c r="V20" s="71" t="n"/>
+      <c r="W20" s="71" t="n"/>
+      <c r="X20" s="71" t="n"/>
+      <c r="Y20" s="71" t="n"/>
+      <c r="Z20" s="71" t="n"/>
+      <c r="AA20" s="71" t="n"/>
+      <c r="AB20" s="71" t="n"/>
+      <c r="AC20" s="71" t="n"/>
+      <c r="AD20" s="71" t="n"/>
     </row>
     <row r="21" ht="42" customHeight="1" s="64">
-      <c r="B21" s="30" t="n"/>
-      <c r="C21" s="31" t="n"/>
-      <c r="D21" s="31" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="6" t="n"/>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="9" t="n"/>
-      <c r="I21" s="33" t="n"/>
-      <c r="J21" s="7" t="inlineStr">
-        <is>
-          <t>In-progress</t>
-        </is>
-      </c>
-      <c r="K21" s="30" t="n"/>
-      <c r="L21" s="31" t="n"/>
-      <c r="M21" s="31" t="n"/>
-      <c r="N21" s="31" t="n"/>
-      <c r="O21" s="31" t="n"/>
-      <c r="P21" s="31" t="n"/>
-      <c r="Q21" s="31" t="n"/>
-      <c r="R21" s="31" t="n"/>
-      <c r="S21" s="31" t="n"/>
-      <c r="T21" s="31" t="n"/>
-      <c r="U21" s="40" t="n"/>
-      <c r="V21" s="40" t="n"/>
-      <c r="W21" s="40" t="n"/>
-      <c r="X21" s="40" t="n"/>
-      <c r="Y21" s="40" t="n"/>
-      <c r="Z21" s="31" t="n"/>
-      <c r="AA21" s="31" t="n"/>
-      <c r="AB21" s="31" t="n"/>
-      <c r="AC21" s="31" t="n"/>
-      <c r="AD21" s="8" t="n"/>
+      <c r="B21" s="71" t="n"/>
+      <c r="C21" s="71" t="n"/>
+      <c r="D21" s="71" t="n"/>
+      <c r="E21" s="81" t="inlineStr">
+        <is>
+          <t>US-02.03 – Phân tích EDA 10.129 ảnh và Snapshot bất biến</t>
+        </is>
+      </c>
+      <c r="F21" s="73" t="n">
+        <v>46294</v>
+      </c>
+      <c r="G21" s="73" t="n">
+        <v>46294</v>
+      </c>
+      <c r="H21" s="74" t="inlineStr">
+        <is>
+          <t>Vân Anh</t>
+        </is>
+      </c>
+      <c r="I21" s="75" t="inlineStr">
+        <is>
+          <t>Báo cáo EDA, snapshot_20260930_165016, data.yaml</t>
+        </is>
+      </c>
+      <c r="J21" s="76" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
+        </is>
+      </c>
+      <c r="K21" s="71" t="n"/>
+      <c r="L21" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N21" s="71" t="n"/>
+      <c r="O21" s="71" t="n"/>
+      <c r="P21" s="71" t="n"/>
+      <c r="Q21" s="71" t="n"/>
+      <c r="R21" s="71" t="n"/>
+      <c r="S21" s="71" t="n"/>
+      <c r="T21" s="71" t="n"/>
+      <c r="U21" s="80" t="n"/>
+      <c r="V21" s="80" t="n"/>
+      <c r="W21" s="80" t="n"/>
+      <c r="X21" s="80" t="n"/>
+      <c r="Y21" s="80" t="n"/>
+      <c r="Z21" s="71" t="n"/>
+      <c r="AA21" s="71" t="n"/>
+      <c r="AB21" s="71" t="n"/>
+      <c r="AC21" s="71" t="n"/>
+      <c r="AD21" s="71" t="n"/>
     </row>
     <row r="22" ht="42" customHeight="1" s="64">
-      <c r="B22" s="36" t="n"/>
-      <c r="C22" s="31" t="n"/>
-      <c r="D22" s="31" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="6" t="n"/>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="9" t="n"/>
-      <c r="I22" s="33" t="n"/>
-      <c r="J22" s="7" t="inlineStr">
-        <is>
-          <t>In-progress</t>
-        </is>
-      </c>
-      <c r="K22" s="30" t="n"/>
-      <c r="L22" s="31" t="n"/>
-      <c r="M22" s="31" t="n"/>
-      <c r="N22" s="31" t="n"/>
-      <c r="O22" s="31" t="n"/>
-      <c r="P22" s="38" t="n"/>
-      <c r="Q22" s="38" t="n"/>
-      <c r="R22" s="38" t="n"/>
-      <c r="S22" s="38" t="n"/>
-      <c r="T22" s="38" t="n"/>
-      <c r="U22" s="38" t="n"/>
-      <c r="V22" s="38" t="n"/>
-      <c r="W22" s="38" t="n"/>
-      <c r="X22" s="38" t="n"/>
-      <c r="Y22" s="38" t="n"/>
-      <c r="Z22" s="31" t="n"/>
-      <c r="AA22" s="31" t="n"/>
-      <c r="AB22" s="31" t="n"/>
-      <c r="AC22" s="31" t="n"/>
-      <c r="AD22" s="8" t="n"/>
+      <c r="B22" s="70" t="inlineStr">
+        <is>
+          <t>US-03 – Huấn luyện YOLO11, Đánh giá và Đóng gói Candidate</t>
+        </is>
+      </c>
+      <c r="C22" s="71" t="n"/>
+      <c r="D22" s="71" t="n"/>
+      <c r="E22" s="72" t="n"/>
+      <c r="F22" s="73" t="n">
+        <v>46294</v>
+      </c>
+      <c r="G22" s="73" t="n">
+        <v>46297</v>
+      </c>
+      <c r="H22" s="74" t="inlineStr">
+        <is>
+          <t>Nghị + Vân Anh</t>
+        </is>
+      </c>
+      <c r="I22" s="75" t="inlineStr">
+        <is>
+          <t>Candidate 82 lớp hoàn chỉnh (YOLO11n + YOLO11m)</t>
+        </is>
+      </c>
+      <c r="J22" s="76" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
+        </is>
+      </c>
+      <c r="K22" s="71" t="n"/>
+      <c r="L22" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N22" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P22" s="78" t="n"/>
+      <c r="Q22" s="78" t="n"/>
+      <c r="R22" s="78" t="n"/>
+      <c r="S22" s="78" t="n"/>
+      <c r="T22" s="78" t="n"/>
+      <c r="U22" s="78" t="n"/>
+      <c r="V22" s="78" t="n"/>
+      <c r="W22" s="78" t="n"/>
+      <c r="X22" s="78" t="n"/>
+      <c r="Y22" s="78" t="n"/>
+      <c r="Z22" s="71" t="n"/>
+      <c r="AA22" s="71" t="n"/>
+      <c r="AB22" s="71" t="n"/>
+      <c r="AC22" s="71" t="n"/>
+      <c r="AD22" s="71" t="n"/>
     </row>
     <row r="23" ht="42" customHeight="1" s="64">
-      <c r="B23" s="30" t="n"/>
-      <c r="C23" s="31" t="n"/>
-      <c r="D23" s="31" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="6" t="n"/>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="9" t="n"/>
-      <c r="I23" s="33" t="n"/>
-      <c r="J23" s="7" t="inlineStr">
-        <is>
-          <t>In-progress</t>
-        </is>
-      </c>
-      <c r="K23" s="30" t="n"/>
-      <c r="L23" s="31" t="n"/>
-      <c r="M23" s="31" t="n"/>
-      <c r="N23" s="31" t="n"/>
-      <c r="O23" s="31" t="n"/>
-      <c r="P23" s="40" t="n"/>
-      <c r="Q23" s="40" t="n"/>
-      <c r="R23" s="40" t="n"/>
-      <c r="S23" s="40" t="n"/>
-      <c r="T23" s="40" t="n"/>
-      <c r="U23" s="31" t="n"/>
-      <c r="V23" s="31" t="n"/>
-      <c r="W23" s="31" t="n"/>
-      <c r="X23" s="31" t="n"/>
-      <c r="Y23" s="31" t="n"/>
-      <c r="Z23" s="31" t="n"/>
-      <c r="AA23" s="31" t="n"/>
-      <c r="AB23" s="31" t="n"/>
-      <c r="AC23" s="31" t="n"/>
-      <c r="AD23" s="8" t="n"/>
+      <c r="B23" s="71" t="n"/>
+      <c r="C23" s="79" t="inlineStr">
+        <is>
+          <t>US-03.01 – Huấn luyện ngầm 50 epochs &amp; Safe Resume</t>
+        </is>
+      </c>
+      <c r="D23" s="71" t="n"/>
+      <c r="E23" s="72" t="n"/>
+      <c r="F23" s="73" t="n">
+        <v>46294</v>
+      </c>
+      <c r="G23" s="73" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H23" s="74" t="inlineStr">
+        <is>
+          <t>Nghị</t>
+        </is>
+      </c>
+      <c r="I23" s="75" t="inlineStr">
+        <is>
+          <t>Huấn luyện ngầm, workers=0 Windows, best.pt, log</t>
+        </is>
+      </c>
+      <c r="J23" s="76" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
+        </is>
+      </c>
+      <c r="K23" s="71" t="n"/>
+      <c r="L23" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N23" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" s="71" t="n"/>
+      <c r="P23" s="80" t="n"/>
+      <c r="Q23" s="80" t="n"/>
+      <c r="R23" s="80" t="n"/>
+      <c r="S23" s="80" t="n"/>
+      <c r="T23" s="80" t="n"/>
+      <c r="U23" s="71" t="n"/>
+      <c r="V23" s="71" t="n"/>
+      <c r="W23" s="71" t="n"/>
+      <c r="X23" s="71" t="n"/>
+      <c r="Y23" s="71" t="n"/>
+      <c r="Z23" s="71" t="n"/>
+      <c r="AA23" s="71" t="n"/>
+      <c r="AB23" s="71" t="n"/>
+      <c r="AC23" s="71" t="n"/>
+      <c r="AD23" s="71" t="n"/>
     </row>
     <row r="24" ht="42" customHeight="1" s="64">
-      <c r="B24" s="30" t="n"/>
-      <c r="C24" s="31" t="n"/>
-      <c r="D24" s="31" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="6" t="n"/>
-      <c r="G24" s="6" t="n"/>
-      <c r="H24" s="9" t="n"/>
-      <c r="I24" s="33" t="n"/>
-      <c r="J24" s="7" t="inlineStr">
-        <is>
-          <t>In-progress</t>
-        </is>
-      </c>
-      <c r="K24" s="30" t="n"/>
-      <c r="L24" s="31" t="n"/>
-      <c r="M24" s="31" t="n"/>
-      <c r="N24" s="31" t="n"/>
-      <c r="O24" s="31" t="n"/>
-      <c r="P24" s="31" t="n"/>
-      <c r="Q24" s="31" t="n"/>
-      <c r="R24" s="31" t="n"/>
-      <c r="S24" s="40" t="n"/>
-      <c r="T24" s="40" t="n"/>
-      <c r="U24" s="40" t="n"/>
-      <c r="V24" s="40" t="n"/>
-      <c r="W24" s="40" t="n"/>
-      <c r="X24" s="31" t="n"/>
-      <c r="Y24" s="31" t="n"/>
-      <c r="Z24" s="31" t="n"/>
-      <c r="AA24" s="31" t="n"/>
-      <c r="AB24" s="31" t="n"/>
-      <c r="AC24" s="31" t="n"/>
-      <c r="AD24" s="8" t="n"/>
+      <c r="B24" s="71" t="n"/>
+      <c r="C24" s="71" t="n"/>
+      <c r="D24" s="79" t="inlineStr">
+        <is>
+          <t>US-03.02 – Đánh giá độc lập trên tập Test (1.016 ảnh)</t>
+        </is>
+      </c>
+      <c r="E24" s="72" t="n"/>
+      <c r="F24" s="73" t="n">
+        <v>46296</v>
+      </c>
+      <c r="G24" s="73" t="n">
+        <v>46297</v>
+      </c>
+      <c r="H24" s="74" t="inlineStr">
+        <is>
+          <t>Nghị + Vân Anh</t>
+        </is>
+      </c>
+      <c r="I24" s="75" t="inlineStr">
+        <is>
+          <t>mAP50=98.03%, F1=96.22%, P=96.16%, R=96.28%</t>
+        </is>
+      </c>
+      <c r="J24" s="76" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
+        </is>
+      </c>
+      <c r="K24" s="71" t="n"/>
+      <c r="L24" s="71" t="n"/>
+      <c r="M24" s="71" t="n"/>
+      <c r="N24" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O24" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P24" s="71" t="n"/>
+      <c r="Q24" s="71" t="n"/>
+      <c r="R24" s="71" t="n"/>
+      <c r="S24" s="80" t="n"/>
+      <c r="T24" s="80" t="n"/>
+      <c r="U24" s="80" t="n"/>
+      <c r="V24" s="80" t="n"/>
+      <c r="W24" s="80" t="n"/>
+      <c r="X24" s="71" t="n"/>
+      <c r="Y24" s="71" t="n"/>
+      <c r="Z24" s="71" t="n"/>
+      <c r="AA24" s="71" t="n"/>
+      <c r="AB24" s="71" t="n"/>
+      <c r="AC24" s="71" t="n"/>
+      <c r="AD24" s="71" t="n"/>
     </row>
     <row r="25" ht="42" customHeight="1" s="64">
-      <c r="B25" s="30" t="n"/>
-      <c r="C25" s="31" t="n"/>
-      <c r="D25" s="31" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="6" t="n"/>
-      <c r="G25" s="6" t="n"/>
-      <c r="H25" s="9" t="n"/>
-      <c r="I25" s="33" t="n"/>
-      <c r="J25" s="7" t="inlineStr">
-        <is>
-          <t>In-progress</t>
-        </is>
-      </c>
-      <c r="K25" s="30" t="n"/>
-      <c r="L25" s="31" t="n"/>
-      <c r="M25" s="31" t="n"/>
-      <c r="N25" s="31" t="n"/>
-      <c r="O25" s="31" t="n"/>
-      <c r="P25" s="31" t="n"/>
-      <c r="Q25" s="31" t="n"/>
-      <c r="R25" s="31" t="n"/>
-      <c r="S25" s="31" t="n"/>
-      <c r="T25" s="31" t="n"/>
-      <c r="U25" s="40" t="n"/>
-      <c r="V25" s="40" t="n"/>
-      <c r="W25" s="40" t="n"/>
-      <c r="X25" s="40" t="n"/>
-      <c r="Y25" s="40" t="n"/>
-      <c r="Z25" s="31" t="n"/>
-      <c r="AA25" s="31" t="n"/>
-      <c r="AB25" s="31" t="n"/>
-      <c r="AC25" s="31" t="n"/>
-      <c r="AD25" s="8" t="n"/>
+      <c r="B25" s="71" t="n"/>
+      <c r="C25" s="71" t="n"/>
+      <c r="D25" s="71" t="n"/>
+      <c r="E25" s="81" t="inlineStr">
+        <is>
+          <t>US-03.03 – Xuất ONNX, Parity Gate &amp; CPU Benchmark</t>
+        </is>
+      </c>
+      <c r="F25" s="73" t="n">
+        <v>46296</v>
+      </c>
+      <c r="G25" s="73" t="n">
+        <v>46297</v>
+      </c>
+      <c r="H25" s="74" t="inlineStr">
+        <is>
+          <t>Nghị + Nam</t>
+        </is>
+      </c>
+      <c r="I25" s="75" t="inlineStr">
+        <is>
+          <t>ONNX tĩnh diff=0.000854 &lt;= 1e-3, latency/FPS đo đạc</t>
+        </is>
+      </c>
+      <c r="J25" s="76" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
+        </is>
+      </c>
+      <c r="K25" s="71" t="n"/>
+      <c r="L25" s="71" t="n"/>
+      <c r="M25" s="71" t="n"/>
+      <c r="N25" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P25" s="71" t="n"/>
+      <c r="Q25" s="71" t="n"/>
+      <c r="R25" s="71" t="n"/>
+      <c r="S25" s="71" t="n"/>
+      <c r="T25" s="71" t="n"/>
+      <c r="U25" s="80" t="n"/>
+      <c r="V25" s="80" t="n"/>
+      <c r="W25" s="80" t="n"/>
+      <c r="X25" s="80" t="n"/>
+      <c r="Y25" s="80" t="n"/>
+      <c r="Z25" s="71" t="n"/>
+      <c r="AA25" s="71" t="n"/>
+      <c r="AB25" s="71" t="n"/>
+      <c r="AC25" s="71" t="n"/>
+      <c r="AD25" s="71" t="n"/>
     </row>
     <row r="26" ht="42" customHeight="1" s="64">
-      <c r="B26" s="36" t="n"/>
-      <c r="C26" s="31" t="n"/>
-      <c r="D26" s="31" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="6" t="n"/>
-      <c r="G26" s="6" t="n"/>
-      <c r="H26" s="9" t="n"/>
-      <c r="I26" s="33" t="n"/>
-      <c r="J26" s="7" t="inlineStr">
-        <is>
-          <t>In-progress</t>
-        </is>
-      </c>
-      <c r="K26" s="30" t="n"/>
-      <c r="L26" s="31" t="n"/>
-      <c r="M26" s="31" t="n"/>
-      <c r="N26" s="31" t="n"/>
-      <c r="O26" s="31" t="n"/>
-      <c r="P26" s="31" t="n"/>
-      <c r="Q26" s="31" t="n"/>
-      <c r="R26" s="31" t="n"/>
-      <c r="S26" s="31" t="n"/>
-      <c r="T26" s="31" t="n"/>
-      <c r="U26" s="31" t="n"/>
-      <c r="V26" s="31" t="n"/>
-      <c r="W26" s="31" t="n"/>
-      <c r="X26" s="31" t="n"/>
-      <c r="Y26" s="31" t="n"/>
-      <c r="Z26" s="38" t="n"/>
-      <c r="AA26" s="38" t="n"/>
-      <c r="AB26" s="38" t="n"/>
-      <c r="AC26" s="38" t="n"/>
-      <c r="AD26" s="41" t="n"/>
+      <c r="B26" s="70" t="inlineStr">
+        <is>
+          <t>US-04 – Thăng cấp Production, Kiểm thử và Bàn giao</t>
+        </is>
+      </c>
+      <c r="C26" s="71" t="n"/>
+      <c r="D26" s="71" t="n"/>
+      <c r="E26" s="72" t="n"/>
+      <c r="F26" s="73" t="n">
+        <v>46295</v>
+      </c>
+      <c r="G26" s="73" t="n">
+        <v>46298</v>
+      </c>
+      <c r="H26" s="74" t="inlineStr">
+        <is>
+          <t>Cả nhóm</t>
+        </is>
+      </c>
+      <c r="I26" s="75" t="inlineStr">
+        <is>
+          <t>Production verified, 215 tests xanh, hồ sơ bàn giao</t>
+        </is>
+      </c>
+      <c r="J26" s="76" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
+        </is>
+      </c>
+      <c r="K26" s="71" t="n"/>
+      <c r="L26" s="71" t="n"/>
+      <c r="M26" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N26" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O26" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P26" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q26" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="R26" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S26" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="U26" s="71" t="n"/>
+      <c r="V26" s="71" t="n"/>
+      <c r="W26" s="71" t="n"/>
+      <c r="X26" s="71" t="n"/>
+      <c r="Y26" s="71" t="n"/>
+      <c r="Z26" s="78" t="n"/>
+      <c r="AA26" s="78" t="n"/>
+      <c r="AB26" s="78" t="n"/>
+      <c r="AC26" s="78" t="n"/>
+      <c r="AD26" s="78" t="n"/>
     </row>
     <row r="27" ht="42" customHeight="1" s="64">
-      <c r="B27" s="30" t="n"/>
-      <c r="C27" s="31" t="n"/>
-      <c r="D27" s="31" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="6" t="n"/>
-      <c r="G27" s="6" t="n"/>
-      <c r="H27" s="9" t="n"/>
-      <c r="I27" s="33" t="n"/>
-      <c r="J27" s="7" t="inlineStr">
-        <is>
-          <t>In-progress</t>
-        </is>
-      </c>
-      <c r="K27" s="30" t="n"/>
-      <c r="L27" s="31" t="n"/>
-      <c r="M27" s="31" t="n"/>
-      <c r="N27" s="31" t="n"/>
-      <c r="O27" s="31" t="n"/>
-      <c r="P27" s="31" t="n"/>
-      <c r="Q27" s="31" t="n"/>
-      <c r="R27" s="31" t="n"/>
-      <c r="S27" s="31" t="n"/>
-      <c r="T27" s="31" t="n"/>
-      <c r="U27" s="31" t="n"/>
-      <c r="V27" s="31" t="n"/>
-      <c r="W27" s="31" t="n"/>
-      <c r="X27" s="31" t="n"/>
-      <c r="Y27" s="31" t="n"/>
-      <c r="Z27" s="40" t="n"/>
-      <c r="AA27" s="40" t="n"/>
-      <c r="AB27" s="40" t="n"/>
-      <c r="AC27" s="31" t="n"/>
-      <c r="AD27" s="8" t="n"/>
+      <c r="B27" s="71" t="n"/>
+      <c r="C27" s="79" t="inlineStr">
+        <is>
+          <t>US-04.01 – Thăng cấp an toàn Safe Atomic Swap &amp; Rollback</t>
+        </is>
+      </c>
+      <c r="D27" s="71" t="n"/>
+      <c r="E27" s="72" t="n"/>
+      <c r="F27" s="73" t="n">
+        <v>46296</v>
+      </c>
+      <c r="G27" s="73" t="n">
+        <v>46297</v>
+      </c>
+      <c r="H27" s="74" t="inlineStr">
+        <is>
+          <t>Nam + Nghị</t>
+        </is>
+      </c>
+      <c r="I27" s="75" t="inlineStr">
+        <is>
+          <t>Thăng cấp YOLO11m lên prod, sao lưu &amp; rollback 1-click</t>
+        </is>
+      </c>
+      <c r="J27" s="76" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
+        </is>
+      </c>
+      <c r="K27" s="71" t="n"/>
+      <c r="L27" s="71" t="n"/>
+      <c r="M27" s="71" t="n"/>
+      <c r="N27" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O27" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P27" s="71" t="n"/>
+      <c r="Q27" s="71" t="n"/>
+      <c r="R27" s="71" t="n"/>
+      <c r="S27" s="71" t="n"/>
+      <c r="T27" s="71" t="n"/>
+      <c r="U27" s="71" t="n"/>
+      <c r="V27" s="71" t="n"/>
+      <c r="W27" s="71" t="n"/>
+      <c r="X27" s="71" t="n"/>
+      <c r="Y27" s="71" t="n"/>
+      <c r="Z27" s="80" t="n"/>
+      <c r="AA27" s="80" t="n"/>
+      <c r="AB27" s="80" t="n"/>
+      <c r="AC27" s="71" t="n"/>
+      <c r="AD27" s="71" t="n"/>
     </row>
     <row r="28" ht="42" customHeight="1" s="64">
-      <c r="B28" s="30" t="n"/>
-      <c r="C28" s="31" t="n"/>
-      <c r="D28" s="31" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="6" t="n"/>
-      <c r="G28" s="6" t="n"/>
-      <c r="H28" s="9" t="n"/>
-      <c r="I28" s="33" t="n"/>
-      <c r="J28" s="7" t="inlineStr">
-        <is>
-          <t>In-progress</t>
-        </is>
-      </c>
-      <c r="K28" s="30" t="n"/>
-      <c r="L28" s="31" t="n"/>
-      <c r="M28" s="31" t="n"/>
-      <c r="N28" s="31" t="n"/>
-      <c r="O28" s="31" t="n"/>
-      <c r="P28" s="31" t="n"/>
-      <c r="Q28" s="31" t="n"/>
-      <c r="R28" s="31" t="n"/>
-      <c r="S28" s="31" t="n"/>
-      <c r="T28" s="31" t="n"/>
-      <c r="U28" s="31" t="n"/>
-      <c r="V28" s="31" t="n"/>
-      <c r="W28" s="31" t="n"/>
-      <c r="X28" s="31" t="n"/>
-      <c r="Y28" s="31" t="n"/>
-      <c r="Z28" s="31" t="n"/>
-      <c r="AA28" s="31" t="n"/>
-      <c r="AB28" s="40" t="n"/>
-      <c r="AC28" s="40" t="n"/>
-      <c r="AD28" s="8" t="n"/>
+      <c r="B28" s="71" t="n"/>
+      <c r="C28" s="71" t="n"/>
+      <c r="D28" s="79" t="inlineStr">
+        <is>
+          <t>US-04.02 – Bộ kiểm thử hồi quy tự động 215 tests pytest</t>
+        </is>
+      </c>
+      <c r="E28" s="72" t="n"/>
+      <c r="F28" s="73" t="n">
+        <v>46295</v>
+      </c>
+      <c r="G28" s="73" t="n">
+        <v>46297</v>
+      </c>
+      <c r="H28" s="74" t="inlineStr">
+        <is>
+          <t>Điệp + Nam</t>
+        </is>
+      </c>
+      <c r="I28" s="75" t="inlineStr">
+        <is>
+          <t>215/215 tests xanh (213 passed, 2 skipped)</t>
+        </is>
+      </c>
+      <c r="J28" s="76" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
+        </is>
+      </c>
+      <c r="K28" s="71" t="n"/>
+      <c r="L28" s="71" t="n"/>
+      <c r="M28" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N28" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O28" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P28" s="71" t="n"/>
+      <c r="Q28" s="71" t="n"/>
+      <c r="R28" s="71" t="n"/>
+      <c r="S28" s="71" t="n"/>
+      <c r="T28" s="71" t="n"/>
+      <c r="U28" s="71" t="n"/>
+      <c r="V28" s="71" t="n"/>
+      <c r="W28" s="71" t="n"/>
+      <c r="X28" s="71" t="n"/>
+      <c r="Y28" s="71" t="n"/>
+      <c r="Z28" s="71" t="n"/>
+      <c r="AA28" s="71" t="n"/>
+      <c r="AB28" s="80" t="n"/>
+      <c r="AC28" s="80" t="n"/>
+      <c r="AD28" s="71" t="n"/>
     </row>
     <row r="29" ht="42" customHeight="1" s="64">
-      <c r="B29" s="30" t="n"/>
-      <c r="C29" s="31" t="n"/>
-      <c r="D29" s="31" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="6" t="n"/>
-      <c r="G29" s="6" t="n"/>
-      <c r="H29" s="9" t="n"/>
-      <c r="I29" s="33" t="n"/>
-      <c r="J29" s="7" t="inlineStr">
-        <is>
-          <t>In-progress</t>
-        </is>
-      </c>
-      <c r="K29" s="30" t="n"/>
-      <c r="L29" s="31" t="n"/>
-      <c r="M29" s="31" t="n"/>
-      <c r="N29" s="31" t="n"/>
-      <c r="O29" s="31" t="n"/>
-      <c r="P29" s="31" t="n"/>
-      <c r="Q29" s="31" t="n"/>
-      <c r="R29" s="31" t="n"/>
-      <c r="S29" s="31" t="n"/>
-      <c r="T29" s="31" t="n"/>
-      <c r="U29" s="31" t="n"/>
-      <c r="V29" s="31" t="n"/>
-      <c r="W29" s="31" t="n"/>
-      <c r="X29" s="31" t="n"/>
-      <c r="Y29" s="31" t="n"/>
-      <c r="Z29" s="31" t="n"/>
-      <c r="AA29" s="31" t="n"/>
-      <c r="AB29" s="31" t="n"/>
-      <c r="AC29" s="40" t="n"/>
-      <c r="AD29" s="42" t="n"/>
+      <c r="B29" s="71" t="n"/>
+      <c r="C29" s="71" t="n"/>
+      <c r="D29" s="71" t="n"/>
+      <c r="E29" s="81" t="inlineStr">
+        <is>
+          <t>US-04.03 – Hồ sơ bàn giao, Slide bảo vệ, Q&amp;A và Báo cáo</t>
+        </is>
+      </c>
+      <c r="F29" s="73" t="n">
+        <v>46296</v>
+      </c>
+      <c r="G29" s="73" t="n">
+        <v>46298</v>
+      </c>
+      <c r="H29" s="74" t="inlineStr">
+        <is>
+          <t>Cả nhóm</t>
+        </is>
+      </c>
+      <c r="I29" s="75" t="inlineStr">
+        <is>
+          <t>HDSD, 14 slides bảo vệ, Cẩm nang Q&amp;A, Báo cáo dự án</t>
+        </is>
+      </c>
+      <c r="J29" s="76" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
+        </is>
+      </c>
+      <c r="K29" s="71" t="n"/>
+      <c r="L29" s="71" t="n"/>
+      <c r="M29" s="71" t="n"/>
+      <c r="N29" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O29" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P29" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q29" s="71" t="n"/>
+      <c r="R29" s="71" t="n"/>
+      <c r="S29" s="71" t="n"/>
+      <c r="T29" s="71" t="n"/>
+      <c r="U29" s="71" t="n"/>
+      <c r="V29" s="71" t="n"/>
+      <c r="W29" s="71" t="n"/>
+      <c r="X29" s="71" t="n"/>
+      <c r="Y29" s="71" t="n"/>
+      <c r="Z29" s="71" t="n"/>
+      <c r="AA29" s="71" t="n"/>
+      <c r="AB29" s="71" t="n"/>
+      <c r="AC29" s="80" t="n"/>
+      <c r="AD29" s="80" t="n"/>
     </row>
     <row r="30" ht="42" customHeight="1" s="64">
-      <c r="B30" s="30" t="n"/>
-      <c r="C30" s="31" t="n"/>
-      <c r="D30" s="31" t="n"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="9" t="n"/>
-      <c r="G30" s="9" t="n"/>
-      <c r="H30" s="9" t="n"/>
-      <c r="I30" s="34" t="n"/>
-      <c r="J30" s="7" t="n"/>
-      <c r="K30" s="30" t="n"/>
-      <c r="L30" s="31" t="n"/>
-      <c r="M30" s="31" t="n"/>
-      <c r="N30" s="31" t="n"/>
-      <c r="O30" s="31" t="n"/>
-      <c r="P30" s="31" t="n"/>
-      <c r="Q30" s="31" t="n"/>
-      <c r="R30" s="31" t="n"/>
-      <c r="S30" s="31" t="n"/>
-      <c r="T30" s="31" t="n"/>
-      <c r="U30" s="31" t="n"/>
-      <c r="V30" s="31" t="n"/>
-      <c r="W30" s="31" t="n"/>
-      <c r="X30" s="31" t="n"/>
-      <c r="Y30" s="31" t="n"/>
-      <c r="Z30" s="31" t="n"/>
-      <c r="AA30" s="31" t="n"/>
-      <c r="AB30" s="31" t="n"/>
-      <c r="AC30" s="31" t="n"/>
-      <c r="AD30" s="42" t="n"/>
+      <c r="B30" s="70" t="inlineStr">
+        <is>
+          <t>US-05 – Định hướng nâng cấp và mở rộng sau bàn giao</t>
+        </is>
+      </c>
+      <c r="C30" s="71" t="n"/>
+      <c r="D30" s="71" t="n"/>
+      <c r="E30" s="72" t="n"/>
+      <c r="F30" s="73" t="n">
+        <v>46307</v>
+      </c>
+      <c r="G30" s="73" t="n">
+        <v>46318</v>
+      </c>
+      <c r="H30" s="74" t="inlineStr">
+        <is>
+          <t>Nam + Nghị</t>
+        </is>
+      </c>
+      <c r="I30" s="74" t="inlineStr">
+        <is>
+          <t>RTSP camera trực tiếp, cảnh báo giọng nói, GPS</t>
+        </is>
+      </c>
+      <c r="J30" s="82" t="inlineStr">
+        <is>
+          <t>Đang nghiên cứu</t>
+        </is>
+      </c>
+      <c r="K30" s="71" t="n"/>
+      <c r="L30" s="71" t="n"/>
+      <c r="M30" s="71" t="n"/>
+      <c r="N30" s="71" t="n"/>
+      <c r="O30" s="71" t="n"/>
+      <c r="P30" s="71" t="n"/>
+      <c r="Q30" s="71" t="n"/>
+      <c r="R30" s="71" t="n"/>
+      <c r="S30" s="71" t="n"/>
+      <c r="T30" s="71" t="n"/>
+      <c r="U30" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="V30" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="W30" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X30" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Y30" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Z30" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AA30" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AB30" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AC30" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AD30" s="77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="B31" s="30" t="n"/>
